--- a/data/trans_dic/P26-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P26-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,06; 25,79</t>
+          <t>17,98; 26,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,26; 33,76</t>
+          <t>23,93; 34,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,09; 23,61</t>
+          <t>14,91; 23,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 12,14</t>
+          <t>6,41; 12,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,98; 33,2</t>
+          <t>22,38; 33,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,99; 38,24</t>
+          <t>26,22; 38,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,49; 28,39</t>
+          <t>18,92; 28,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,91</t>
+          <t>7,81; 13,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,98; 27,52</t>
+          <t>20,77; 27,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,27; 33,87</t>
+          <t>26,43; 33,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,78; 23,98</t>
+          <t>17,7; 24,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 11,93</t>
+          <t>7,7; 11,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 27,77</t>
+          <t>18,43; 27,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,85; 31,69</t>
+          <t>21,61; 31,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,9; 24,11</t>
+          <t>15,84; 24,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,98</t>
+          <t>6,23; 14,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,08; 41,19</t>
+          <t>31,35; 41,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,68; 37,54</t>
+          <t>27,15; 37,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,3; 27,64</t>
+          <t>18,77; 28,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 16,07</t>
+          <t>9,69; 16,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,2; 33,18</t>
+          <t>26,08; 33,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,88; 32,84</t>
+          <t>25,5; 32,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 24,76</t>
+          <t>18,68; 24,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,66; 13,91</t>
+          <t>8,51; 13,4</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,11; 32,01</t>
+          <t>24,55; 32,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,06; 37,94</t>
+          <t>30,06; 37,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,7; 30,18</t>
+          <t>21,87; 30,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 80,46</t>
+          <t>7,56; 78,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,08; 52,26</t>
+          <t>36,08; 51,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,28; 49,87</t>
+          <t>37,32; 50,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,41; 30,04</t>
+          <t>15,59; 29,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 12,9</t>
+          <t>5,36; 12,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,3; 35,48</t>
+          <t>28,46; 35,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,24; 40,14</t>
+          <t>33,47; 40,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,28; 28,45</t>
+          <t>21,07; 28,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 72,03</t>
+          <t>7,77; 74,41</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,31; 30,47</t>
+          <t>25,33; 30,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,4; 36,36</t>
+          <t>30,33; 36,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,53; 29,69</t>
+          <t>24,45; 29,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 16,53</t>
+          <t>10,95; 16,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,76; 45,64</t>
+          <t>37,99; 45,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,28; 45,7</t>
+          <t>38,38; 45,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,62; 33,03</t>
+          <t>26,82; 33,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 19,3</t>
+          <t>6,49; 19,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,81; 35,35</t>
+          <t>30,77; 35,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,56; 39,3</t>
+          <t>34,31; 39,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,15; 30,39</t>
+          <t>26,06; 30,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 16,35</t>
+          <t>9,12; 16,33</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,16; 37,4</t>
+          <t>27,55; 38,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,61; 37,67</t>
+          <t>28,8; 37,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,62; 27,88</t>
+          <t>20,91; 27,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,72</t>
+          <t>10,47; 17,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,48; 49,17</t>
+          <t>39,57; 48,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,12; 44,96</t>
+          <t>37,44; 44,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 33,89</t>
+          <t>27,15; 33,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 16,51</t>
+          <t>9,94; 16,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,45; 43,26</t>
+          <t>36,31; 43,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,02; 40,62</t>
+          <t>34,97; 40,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,07; 30,1</t>
+          <t>25,1; 30,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,3</t>
+          <t>11,19; 16,08</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,71; 51,07</t>
+          <t>39,16; 50,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36,86; 48,47</t>
+          <t>36,7; 48,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,53; 41,0</t>
+          <t>29,12; 40,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 24,97</t>
+          <t>8,59; 25,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,93; 35,41</t>
+          <t>30,11; 35,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,85; 41,12</t>
+          <t>34,88; 41,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,24; 27,69</t>
+          <t>21,74; 27,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 16,03</t>
+          <t>9,81; 16,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,75; 37,83</t>
+          <t>32,89; 38,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36,12; 41,78</t>
+          <t>35,95; 41,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,42; 29,54</t>
+          <t>24,33; 29,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,59; 16,33</t>
+          <t>10,34; 16,1</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,86; 30,27</t>
+          <t>26,98; 30,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,17; 34,47</t>
+          <t>31,17; 34,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,53; 26,86</t>
+          <t>23,67; 26,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,18; 41,73</t>
+          <t>11,15; 39,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,23; 38,75</t>
+          <t>35,37; 38,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,98; 40,43</t>
+          <t>36,94; 40,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,01; 28,12</t>
+          <t>25,11; 28,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,28</t>
+          <t>10,46; 14,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,14</t>
+          <t>31,76; 34,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34,67; 37,06</t>
+          <t>34,54; 37,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,79; 27,02</t>
+          <t>24,75; 27,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,85; 25,32</t>
+          <t>11,76; 27,81</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79791; 113978</t>
+          <t>79437; 115381</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97816; 136082</t>
+          <t>96449; 137144</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57457; 89908</t>
+          <t>56781; 88310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28990; 56448</t>
+          <t>29814; 57670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60904; 91986</t>
+          <t>62006; 91966</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76284; 112215</t>
+          <t>76942; 112106</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58688; 90113</t>
+          <t>60059; 89100</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31547; 53461</t>
+          <t>32341; 54126</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>150836; 197860</t>
+          <t>149346; 195537</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>182995; 235902</t>
+          <t>184089; 234527</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>124163; 167434</t>
+          <t>123604; 168563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>67801; 104888</t>
+          <t>67714; 102757</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61057; 91850</t>
+          <t>60957; 92329</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88009; 127616</t>
+          <t>87037; 126439</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56485; 85654</t>
+          <t>56292; 86825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25610; 54168</t>
+          <t>25978; 58870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>108947; 144421</t>
+          <t>109900; 145973</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86205; 121314</t>
+          <t>87743; 122145</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62604; 94536</t>
+          <t>64205; 97713</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34955; 57744</t>
+          <t>34807; 59064</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178540; 226091</t>
+          <t>177721; 227059</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>187878; 238346</t>
+          <t>185074; 238326</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128176; 172679</t>
+          <t>130252; 172925</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67247; 107966</t>
+          <t>66085; 104048</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>124088; 164724</t>
+          <t>126330; 165797</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>182712; 230592</t>
+          <t>182659; 228832</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105826; 147199</t>
+          <t>106687; 146391</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47703; 506699</t>
+          <t>47633; 493456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56147; 81335</t>
+          <t>56155; 80205</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89635; 119916</t>
+          <t>89731; 120728</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23597; 46015</t>
+          <t>23872; 44788</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8105; 19196</t>
+          <t>7973; 19158</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>189702; 237828</t>
+          <t>190741; 237120</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>281901; 340441</t>
+          <t>283917; 340303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>136376; 182335</t>
+          <t>135074; 181607</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60719; 560796</t>
+          <t>60505; 579342</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>290889; 350213</t>
+          <t>291060; 351219</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>336007; 401971</t>
+          <t>335317; 400254</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>264476; 320135</t>
+          <t>263681; 321480</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100704; 153330</t>
+          <t>101631; 151686</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>251338; 303803</t>
+          <t>252919; 302925</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>285318; 340573</t>
+          <t>286004; 339583</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>205089; 254462</t>
+          <t>206654; 258990</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69243; 178272</t>
+          <t>59946; 176237</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>559105; 641664</t>
+          <t>558526; 637793</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>639604; 727338</t>
+          <t>634926; 722785</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>483370; 561841</t>
+          <t>481807; 560144</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>173885; 302677</t>
+          <t>168884; 302248</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86095; 118557</t>
+          <t>87336; 120641</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>140920; 185565</t>
+          <t>141882; 184975</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115341; 155932</t>
+          <t>116986; 156103</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44516; 74743</t>
+          <t>44162; 74531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>209475; 254419</t>
+          <t>204731; 252401</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>269261; 326164</t>
+          <t>271588; 325471</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>185720; 232855</t>
+          <t>186533; 232979</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>76733; 127419</t>
+          <t>76746; 126755</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>304179; 360972</t>
+          <t>302977; 359372</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>426544; 494784</t>
+          <t>425920; 494809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>312516; 375127</t>
+          <t>312863; 375112</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>132287; 194576</t>
+          <t>133535; 191929</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>115892; 149047</t>
+          <t>114289; 147847</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>97324; 127997</t>
+          <t>96917; 128142</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82962; 115167</t>
+          <t>81810; 113818</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18479; 56905</t>
+          <t>19582; 57138</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>336711; 398276</t>
+          <t>338656; 395735</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>357893; 422279</t>
+          <t>358209; 422047</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>222470; 276962</t>
+          <t>217467; 275182</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64714; 107222</t>
+          <t>65627; 107036</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>463964; 535907</t>
+          <t>466027; 539178</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>466336; 539402</t>
+          <t>464156; 534509</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>312851; 378446</t>
+          <t>311666; 378977</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>94986; 146469</t>
+          <t>92752; 144375</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>817906; 921824</t>
+          <t>821569; 918171</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1020993; 1129024</t>
+          <t>1021170; 1133224</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>739412; 843983</t>
+          <t>743845; 839472</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>345463; 1289217</t>
+          <t>344351; 1232840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1089181; 1197981</t>
+          <t>1093542; 1198857</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1240534; 1356262</t>
+          <t>1239312; 1354725</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>818088; 919717</t>
+          <t>821065; 925357</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>329842; 469362</t>
+          <t>343902; 470313</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1941066; 2094859</t>
+          <t>1948832; 2095516</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2298569; 2457377</t>
+          <t>2289821; 2457704</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1589391; 1732406</t>
+          <t>1587033; 1732832</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>755238; 1614244</t>
+          <t>749560; 1773213</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P26-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P26-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,98; 26,11</t>
+          <t>18,36; 26,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,93; 34,02</t>
+          <t>24,47; 34,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 23,19</t>
+          <t>14,96; 22,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,4</t>
+          <t>6,75; 12,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,38; 33,19</t>
+          <t>22,6; 33,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,22; 38,2</t>
+          <t>26,26; 37,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,92; 28,07</t>
+          <t>18,67; 28,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,07</t>
+          <t>7,68; 13,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,77; 27,2</t>
+          <t>20,96; 27,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,43; 33,67</t>
+          <t>26,38; 33,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,7; 24,14</t>
+          <t>17,88; 23,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,69</t>
+          <t>7,82; 11,69</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,43; 27,91</t>
+          <t>17,91; 28,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,61; 31,4</t>
+          <t>22,33; 31,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 24,44</t>
+          <t>16,43; 24,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 14,11</t>
+          <t>5,49; 11,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,35; 41,64</t>
+          <t>31,11; 41,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,15; 37,8</t>
+          <t>26,48; 38,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 28,56</t>
+          <t>18,5; 27,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 16,44</t>
+          <t>9,82; 15,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,08; 33,32</t>
+          <t>26,16; 33,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,5; 32,83</t>
+          <t>25,49; 32,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 24,8</t>
+          <t>18,84; 24,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,4</t>
+          <t>8,18; 12,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,55; 32,22</t>
+          <t>24,23; 32,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,06; 37,65</t>
+          <t>30,29; 37,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,87; 30,01</t>
+          <t>21,82; 30,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 78,35</t>
+          <t>6,46; 12,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,08; 51,53</t>
+          <t>36,01; 51,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,32; 50,21</t>
+          <t>36,16; 49,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,59; 29,24</t>
+          <t>15,03; 28,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 12,87</t>
+          <t>5,41; 13,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,46; 35,38</t>
+          <t>28,28; 35,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,47; 40,12</t>
+          <t>33,28; 40,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,07; 28,34</t>
+          <t>21,52; 28,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 74,41</t>
+          <t>6,65; 11,06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,33; 30,56</t>
+          <t>25,18; 30,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,33; 36,21</t>
+          <t>30,56; 36,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,45; 29,82</t>
+          <t>24,52; 29,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 16,35</t>
+          <t>10,89; 15,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,99; 45,51</t>
+          <t>38,05; 45,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,38; 45,56</t>
+          <t>38,68; 45,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,82; 33,62</t>
+          <t>26,74; 33,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 19,08</t>
+          <t>15,55; 20,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,77; 35,14</t>
+          <t>30,56; 34,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,31; 39,06</t>
+          <t>34,62; 39,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,06; 30,3</t>
+          <t>26,14; 30,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,12; 16,33</t>
+          <t>13,38; 17,28</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,55; 38,05</t>
+          <t>27,46; 37,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,8; 37,55</t>
+          <t>28,68; 37,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,91; 27,91</t>
+          <t>20,62; 28,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 17,67</t>
+          <t>10,96; 17,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,57; 48,78</t>
+          <t>39,66; 48,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,44; 44,87</t>
+          <t>37,15; 44,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,15; 33,91</t>
+          <t>26,72; 33,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 16,43</t>
+          <t>13,21; 17,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,31; 43,07</t>
+          <t>36,13; 43,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,97; 40,63</t>
+          <t>35,26; 40,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,1; 30,1</t>
+          <t>25,15; 30,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,08</t>
+          <t>13,06; 16,94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,16; 50,66</t>
+          <t>39,5; 50,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36,7; 48,53</t>
+          <t>37,08; 49,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,12; 40,52</t>
+          <t>29,04; 41,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,59; 25,08</t>
+          <t>8,03; 23,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,11; 35,18</t>
+          <t>29,83; 35,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,88; 41,1</t>
+          <t>35,02; 41,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,74; 27,51</t>
+          <t>22,08; 27,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 16,0</t>
+          <t>9,2; 14,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,89; 38,06</t>
+          <t>32,61; 37,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35,95; 41,4</t>
+          <t>36,33; 41,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,33; 29,58</t>
+          <t>24,54; 29,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 16,1</t>
+          <t>9,87; 14,92</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,98; 30,15</t>
+          <t>26,89; 30,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,17; 34,6</t>
+          <t>31,15; 34,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,67; 26,72</t>
+          <t>23,65; 26,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,15; 39,91</t>
+          <t>10,04; 12,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,37; 38,78</t>
+          <t>35,32; 38,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,94; 40,38</t>
+          <t>36,99; 40,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,11; 28,29</t>
+          <t>25,18; 28,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,46; 14,31</t>
+          <t>12,48; 14,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,76; 34,15</t>
+          <t>31,65; 34,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34,54; 37,07</t>
+          <t>34,67; 37,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,75; 27,02</t>
+          <t>24,91; 27,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,76; 27,81</t>
+          <t>11,7; 13,42</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41987</t>
+          <t>46012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>45553</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83527</t>
+          <t>91565</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79437; 115381</t>
+          <t>81147; 117462</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96449; 137144</t>
+          <t>98635; 137868</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56781; 88310</t>
+          <t>56981; 87325</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29814; 57670</t>
+          <t>34049; 62337</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62006; 91966</t>
+          <t>62623; 91524</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76942; 112106</t>
+          <t>77068; 109872</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60059; 89100</t>
+          <t>59277; 89173</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32341; 54126</t>
+          <t>34630; 58993</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149346; 195537</t>
+          <t>150689; 196778</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>184089; 234527</t>
+          <t>183759; 233826</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123604; 168563</t>
+          <t>124819; 166202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>67714; 102757</t>
+          <t>74754; 111681</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37603</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45712</t>
+          <t>50476</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83316</t>
+          <t>86198</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60957; 92329</t>
+          <t>59254; 93656</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87037; 126439</t>
+          <t>89921; 126465</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56292; 86825</t>
+          <t>58376; 87369</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25978; 58870</t>
+          <t>24422; 51204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>109900; 145973</t>
+          <t>109067; 144328</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87743; 122145</t>
+          <t>85559; 123238</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64205; 97713</t>
+          <t>63280; 95045</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34807; 59064</t>
+          <t>38962; 63430</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>177721; 227059</t>
+          <t>178226; 227458</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>185074; 238326</t>
+          <t>185054; 236596</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>130252; 172925</t>
+          <t>131348; 172606</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66085; 104048</t>
+          <t>68882; 106939</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276948</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>289781</t>
+          <t>52038</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>126330; 165797</t>
+          <t>124681; 165387</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>182659; 228832</t>
+          <t>184090; 229744</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106687; 146391</t>
+          <t>106438; 148234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47633; 493456</t>
+          <t>27836; 52041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56155; 80205</t>
+          <t>56040; 80878</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89731; 120728</t>
+          <t>86947; 119736</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23872; 44788</t>
+          <t>23015; 44409</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7973; 19158</t>
+          <t>9054; 21889</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>190741; 237120</t>
+          <t>189576; 236412</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>283917; 340303</t>
+          <t>282248; 339294</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135074; 181607</t>
+          <t>137921; 183336</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60505; 579342</t>
+          <t>39773; 66182</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123969</t>
+          <t>132901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>131256</t>
+          <t>141192</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>255225</t>
+          <t>274093</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>291060; 351219</t>
+          <t>289413; 349975</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>335317; 400254</t>
+          <t>337823; 404934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>263681; 321480</t>
+          <t>264382; 321158</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>101631; 151686</t>
+          <t>110345; 160696</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>252919; 302925</t>
+          <t>253319; 305293</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>286004; 339583</t>
+          <t>288272; 341554</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>206654; 258990</t>
+          <t>206018; 259616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59946; 176237</t>
+          <t>124322; 161362</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>558526; 637793</t>
+          <t>554713; 634102</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>634926; 722785</t>
+          <t>640636; 728758</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>481807; 560144</t>
+          <t>483267; 562761</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>168884; 302248</t>
+          <t>242548; 313202</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58518</t>
+          <t>69600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>106382</t>
+          <t>115636</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>164900</t>
+          <t>185236</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>87336; 120641</t>
+          <t>87072; 119585</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>141882; 184975</t>
+          <t>141251; 182966</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>116986; 156103</t>
+          <t>115314; 158025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44162; 74531</t>
+          <t>54065; 88014</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>204731; 252401</t>
+          <t>205199; 252185</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>271588; 325471</t>
+          <t>269452; 322988</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>186533; 232979</t>
+          <t>183596; 231671</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>76746; 126755</t>
+          <t>99935; 133747</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>302977; 359372</t>
+          <t>301475; 359250</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>425920; 494809</t>
+          <t>429403; 496038</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>312863; 375112</t>
+          <t>313486; 378306</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>133535; 191929</t>
+          <t>163250; 211743</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34736</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>82990</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>117726</t>
+          <t>118376</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>114289; 147847</t>
+          <t>115295; 148728</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>96917; 128142</t>
+          <t>97906; 130263</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81810; 113818</t>
+          <t>81576; 117094</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19582; 57138</t>
+          <t>18146; 53623</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>338656; 395735</t>
+          <t>335587; 395983</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>358209; 422047</t>
+          <t>359588; 422943</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>217467; 275182</t>
+          <t>220897; 273708</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>65627; 107036</t>
+          <t>68567; 108742</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>466027; 539178</t>
+          <t>461973; 532383</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>464156; 534509</t>
+          <t>468960; 537904</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>311666; 378977</t>
+          <t>314440; 379412</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>92752; 144375</t>
+          <t>95902; 144960</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>573762</t>
+          <t>354352</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>420714</t>
+          <t>453153</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>994475</t>
+          <t>807505</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>821569; 918171</t>
+          <t>818995; 924790</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1021170; 1133224</t>
+          <t>1020251; 1133118</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>743845; 839472</t>
+          <t>743233; 836363</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>344351; 1232840</t>
+          <t>312528; 397242</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1093542; 1198857</t>
+          <t>1091966; 1199766</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1239312; 1354725</t>
+          <t>1240763; 1354744</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>821065; 925357</t>
+          <t>823496; 926852</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>343902; 470313</t>
+          <t>413856; 489416</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1948832; 2095516</t>
+          <t>1942513; 2092189</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2289821; 2457704</t>
+          <t>2298464; 2470917</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1587033; 1732832</t>
+          <t>1597086; 1738674</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>749560; 1773213</t>
+          <t>752155; 863038</t>
         </is>
       </c>
     </row>
